--- a/data/data-mentah/IPM_2023.xlsx
+++ b/data/data-mentah/IPM_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E46F99-8627-4F91-9AAC-F740FBF4DC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB421FEE-1C3B-4C62-B09A-6A589B231ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Kabupaten/Kota</t>
   </si>
@@ -177,12 +177,6 @@
   </si>
   <si>
     <t>80.77</t>
-  </si>
-  <si>
-    <t>Sulawesi Selatan</t>
-  </si>
-  <si>
-    <t>74.6</t>
   </si>
 </sst>
 </file>
@@ -559,10 +553,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -578,7 +572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -586,7 +580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -594,7 +588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -602,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -610,7 +604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -618,7 +612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -626,7 +620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -634,7 +628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -642,7 +636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -650,7 +644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -658,7 +652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -666,7 +660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -674,7 +668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -682,7 +676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -690,7 +684,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -698,7 +692,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -706,7 +700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -714,7 +708,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -722,7 +716,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -730,7 +724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -738,7 +732,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -746,7 +740,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -754,26 +748,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H27" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H26" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>